--- a/B_problem2_results.xlsx
+++ b/B_problem2_results.xlsx
@@ -12,11 +12,13 @@
     <sheet name="03_服务站规模参数" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="04_距离矩阵" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="05_最优选址规模方案" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_小区分配结果" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_服务站覆盖明细" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_年度利润测算" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_总体指标" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_候选方案Top20" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="06_小区需求满足汇总" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_小区到站点分流明细" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_服务站覆盖明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_年度利润测算" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_服务项目收入分摊" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_总体指标" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_模型说明" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +530,23 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>满意度评分规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>求解模型</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>快速MILP：候选小区建站 + 小区需求可拆分</t>
         </is>
       </c>
     </row>
@@ -542,543 +561,3324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>排名</t>
+          <t>小区</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>覆盖老人数</t>
+          <t>服务项目</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>平均满意度</t>
+          <t>月需求</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>服务站</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>占本小区需求比例</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>站点月服务量</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>直接支出</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>直接成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1926.99810774825</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>57809.94323244749</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46247.954585958</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>643</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="F3" t="n">
+        <v>642.9993685947716</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16074.98421486929</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12859.98737189543</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12478</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12477.98774700709</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>124779.8774700709</v>
+      </c>
+      <c r="J4" t="n">
+        <v>99823.90197605672</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2189</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2188.997850472714</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I5" t="n">
+        <v>61291.93981323599</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50346.95056087241</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7976.992166843689</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>159539.8433368738</v>
+      </c>
+      <c r="J6" t="n">
+        <v>127631.874669499</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>506</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="F7" t="n">
+        <v>505.9995031243458</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4047.996024994767</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1612</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1612</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>48360</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38688</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>537</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>537</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13425</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10740</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10393</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10393</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>103930</v>
+      </c>
+      <c r="J10" t="n">
+        <v>83144</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1826</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51128</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6647</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6647</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>132940</v>
+      </c>
+      <c r="J12" t="n">
+        <v>106352</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>456</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1335</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1335.00000000253</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>40050.0000000759</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32040.00000006073</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>445</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="F15" t="n">
+        <v>445.0000000008434</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11125.00000002109</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8900.000000016869</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9047</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9047.000000017148</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>90470.00000017148</v>
+      </c>
+      <c r="J16" t="n">
+        <v>72376.00000013718</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1575.000000002985</v>
+      </c>
+      <c r="G17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" t="n">
+        <v>44100.00000008359</v>
+      </c>
+      <c r="J17" t="n">
+        <v>36225.00000006866</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5757</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5757.000000010911</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>115140.0000002182</v>
+      </c>
+      <c r="J18" t="n">
+        <v>92112.00000017458</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>405</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="F19" t="n">
+        <v>405.0000000007676</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3240.000000006141</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2197</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2197</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24</v>
+      </c>
+      <c r="I20" t="n">
+        <v>65910</v>
+      </c>
+      <c r="J20" t="n">
+        <v>52728</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>732</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>732</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>18300</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14640</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>13826</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13826</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>138260</v>
+      </c>
+      <c r="J22" t="n">
+        <v>110608</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2439</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2439</v>
+      </c>
+      <c r="G23" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23</v>
+      </c>
+      <c r="I23" t="n">
+        <v>68292</v>
+      </c>
+      <c r="J23" t="n">
+        <v>56097</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8864</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8864</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I24" t="n">
+        <v>177280</v>
+      </c>
+      <c r="J24" t="n">
+        <v>141824</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>568</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>568</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="F26" t="n">
+        <v>91.81440568215002</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2754.432170464501</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2203.5457363716</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="F27" t="n">
+        <v>940.1845808765898</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="n">
+        <v>24</v>
+      </c>
+      <c r="I27" t="n">
+        <v>28205.53742629769</v>
+      </c>
+      <c r="J27" t="n">
+        <v>22564.42994103816</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>344</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="F28" t="n">
+        <v>30.60480189405001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" t="n">
+        <v>765.1200473512502</v>
+      </c>
+      <c r="J28" t="n">
+        <v>612.0960378810001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>344</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="F29" t="n">
+        <v>313.3948602921966</v>
+      </c>
+      <c r="G29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7834.871507304915</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6267.897205843932</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7634</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="F30" t="n">
+        <v>679.1774931952841</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6791.774931952841</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5433.419945562273</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7634</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6954.815010089037</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8</v>
+      </c>
+      <c r="I31" t="n">
+        <v>69548.15010089037</v>
+      </c>
+      <c r="J31" t="n">
+        <v>55638.5200807123</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="F32" t="n">
+        <v>116.2804537079167</v>
+      </c>
+      <c r="G32" t="n">
+        <v>28</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3255.852703821668</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2674.450435282085</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1190.718262796224</v>
+      </c>
+      <c r="G33" t="n">
+        <v>28</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23</v>
+      </c>
+      <c r="I33" t="n">
+        <v>33340.11135829426</v>
+      </c>
+      <c r="J33" t="n">
+        <v>27386.52004431315</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4814</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="F34" t="n">
+        <v>428.2892916219673</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="n">
+        <v>16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8565.785832439346</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6852.628665951476</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4814</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4385.705980949519</v>
+      </c>
+      <c r="G35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>87714.11961899037</v>
+      </c>
+      <c r="J35" t="n">
+        <v>70171.2956951923</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>333</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="F36" t="n">
+        <v>29.62615997301934</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>237.0092797841547</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>333</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="F37" t="n">
+        <v>303.3735130154112</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2426.98810412329</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2447</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2375.642802342305</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="n">
+        <v>24</v>
+      </c>
+      <c r="I38" t="n">
+        <v>71269.28407026913</v>
+      </c>
+      <c r="J38" t="n">
+        <v>57015.42725621531</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>815</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="F39" t="n">
+        <v>791.2337081769424</v>
+      </c>
+      <c r="G39" t="n">
+        <v>25</v>
+      </c>
+      <c r="H39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I39" t="n">
+        <v>19780.84270442356</v>
+      </c>
+      <c r="J39" t="n">
+        <v>15824.67416353885</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>15287</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14841.21435202567</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" t="n">
+        <v>8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>148412.1435202567</v>
+      </c>
+      <c r="J40" t="n">
+        <v>118729.7148162053</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2702</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2623.206723305642</v>
+      </c>
+      <c r="G41" t="n">
+        <v>28</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23</v>
+      </c>
+      <c r="I41" t="n">
+        <v>73449.78825255798</v>
+      </c>
+      <c r="J41" t="n">
+        <v>60333.75463602977</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9809</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9522.958826389728</v>
+      </c>
+      <c r="G42" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16</v>
+      </c>
+      <c r="I42" t="n">
+        <v>190459.1765277946</v>
+      </c>
+      <c r="J42" t="n">
+        <v>152367.3412222356</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>626</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="F43" t="n">
+        <v>607.7451549923509</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4861.961239938807</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1390</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1389.999999999932</v>
+      </c>
+      <c r="G44" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24</v>
+      </c>
+      <c r="I44" t="n">
+        <v>41699.99999999795</v>
+      </c>
+      <c r="J44" t="n">
+        <v>33359.99999999836</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>463</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="F45" t="n">
+        <v>462.9999999999771</v>
+      </c>
+      <c r="G45" t="n">
+        <v>25</v>
+      </c>
+      <c r="H45" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" t="n">
+        <v>11574.99999999943</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9259.999999999543</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9568</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9567.999999999529</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>95679.99999999529</v>
+      </c>
+      <c r="J46" t="n">
+        <v>76543.99999999623</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1658.999999999918</v>
+      </c>
+      <c r="G47" t="n">
+        <v>28</v>
+      </c>
+      <c r="H47" t="n">
+        <v>23</v>
+      </c>
+      <c r="I47" t="n">
+        <v>46451.99999999771</v>
+      </c>
+      <c r="J47" t="n">
+        <v>38156.99999999812</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6077</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6076.999999999701</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="n">
+        <v>16</v>
+      </c>
+      <c r="I48" t="n">
+        <v>121539.999999994</v>
+      </c>
+      <c r="J48" t="n">
+        <v>97231.99999999521</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>403</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="F49" t="n">
+        <v>402.9999999999802</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3223.999999999841</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1138.744624749312</v>
+      </c>
+      <c r="G50" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" t="n">
+        <v>24</v>
+      </c>
+      <c r="I50" t="n">
+        <v>34162.33874247937</v>
+      </c>
+      <c r="J50" t="n">
+        <v>27329.8709939835</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="F51" t="n">
+        <v>858.7917459276738</v>
+      </c>
+      <c r="G51" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" t="n">
+        <v>24</v>
+      </c>
+      <c r="I51" t="n">
+        <v>25763.75237783021</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20611.00190226417</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>666</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="F52" t="n">
+        <v>379.5815415831041</v>
+      </c>
+      <c r="G52" t="n">
+        <v>25</v>
+      </c>
+      <c r="H52" t="n">
+        <v>20</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9489.538539577603</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7591.630831662083</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>666</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="F53" t="n">
+        <v>286.2639153092246</v>
+      </c>
+      <c r="G53" t="n">
+        <v>25</v>
+      </c>
+      <c r="H53" t="n">
+        <v>20</v>
+      </c>
+      <c r="I53" t="n">
+        <v>7156.597882730613</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5725.278306184491</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12885</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7343.705950898344</v>
+      </c>
+      <c r="G54" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8</v>
+      </c>
+      <c r="I54" t="n">
+        <v>73437.05950898344</v>
+      </c>
+      <c r="J54" t="n">
+        <v>58749.64760718675</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12885</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5538.304127266304</v>
+      </c>
+      <c r="G55" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" t="n">
+        <v>55383.04127266304</v>
+      </c>
+      <c r="J55" t="n">
+        <v>44306.43301813043</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2261</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1288.639437716814</v>
+      </c>
+      <c r="G56" t="n">
+        <v>28</v>
+      </c>
+      <c r="H56" t="n">
+        <v>23</v>
+      </c>
+      <c r="I56" t="n">
+        <v>36081.9042560708</v>
+      </c>
+      <c r="J56" t="n">
+        <v>29638.70706748673</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2261</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="F57" t="n">
+        <v>971.835904675911</v>
+      </c>
+      <c r="G57" t="n">
+        <v>28</v>
+      </c>
+      <c r="H57" t="n">
+        <v>23</v>
+      </c>
+      <c r="I57" t="n">
+        <v>27211.40533092551</v>
+      </c>
+      <c r="J57" t="n">
+        <v>22352.22580754595</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>8239</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4695.754235890683</v>
+      </c>
+      <c r="G58" t="n">
+        <v>20</v>
+      </c>
+      <c r="H58" t="n">
+        <v>16</v>
+      </c>
+      <c r="I58" t="n">
+        <v>93915.08471781366</v>
+      </c>
+      <c r="J58" t="n">
+        <v>75132.06777425093</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8239</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3541.333931280332</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" t="n">
+        <v>16</v>
+      </c>
+      <c r="I59" t="n">
+        <v>70826.67862560664</v>
+      </c>
+      <c r="J59" t="n">
+        <v>56661.34290048532</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>528</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="F60" t="n">
+        <v>300.9295104442627</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2407.436083554102</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>528</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="F61" t="n">
+        <v>226.9479688937997</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1815.583751150397</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="F62" t="n">
+        <v>312.8979256861301</v>
+      </c>
+      <c r="G62" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" t="n">
+        <v>24</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9386.937770583903</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7509.550216467123</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="F63" t="n">
+        <v>835.8549344158851</v>
+      </c>
+      <c r="G63" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" t="n">
+        <v>24</v>
+      </c>
+      <c r="I63" t="n">
+        <v>25075.64803247655</v>
+      </c>
+      <c r="J63" t="n">
+        <v>20060.51842598124</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>上门护理</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="F64" t="n">
+        <v>551.2471398990714</v>
+      </c>
+      <c r="G64" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" t="n">
+        <v>24</v>
+      </c>
+      <c r="I64" t="n">
+        <v>16537.41419697214</v>
+      </c>
+      <c r="J64" t="n">
+        <v>13229.93135757771</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>567</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="F65" t="n">
+        <v>104.3606610964916</v>
+      </c>
+      <c r="G65" t="n">
+        <v>25</v>
+      </c>
+      <c r="H65" t="n">
+        <v>20</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2609.016527412291</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2087.213221929833</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>567</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="F66" t="n">
+        <v>278.782204596357</v>
+      </c>
+      <c r="G66" t="n">
+        <v>25</v>
+      </c>
+      <c r="H66" t="n">
+        <v>20</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6969.555114908924</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5575.644091927139</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>助浴</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>567</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="F67" t="n">
+        <v>183.8571343075138</v>
+      </c>
+      <c r="G67" t="n">
+        <v>25</v>
+      </c>
+      <c r="H67" t="n">
+        <v>20</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4596.428357687845</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3677.142686150276</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>11331</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2085.55670349973</v>
+      </c>
+      <c r="G68" t="n">
+        <v>10</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" t="n">
+        <v>20855.5670349973</v>
+      </c>
+      <c r="J68" t="n">
+        <v>16684.45362799784</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11331</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5571.218977568466</v>
+      </c>
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8</v>
+      </c>
+      <c r="I69" t="n">
+        <v>55712.18977568467</v>
+      </c>
+      <c r="J69" t="n">
+        <v>44569.75182054773</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>助餐</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>11331</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3674.224318939046</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10</v>
+      </c>
+      <c r="H70" t="n">
+        <v>8</v>
+      </c>
+      <c r="I70" t="n">
+        <v>36742.24318939046</v>
+      </c>
+      <c r="J70" t="n">
+        <v>29393.79455151236</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="F71" t="n">
+        <v>363.6978242092901</v>
+      </c>
+      <c r="G71" t="n">
+        <v>28</v>
+      </c>
+      <c r="H71" t="n">
+        <v>23</v>
+      </c>
+      <c r="I71" t="n">
+        <v>10183.53907786012</v>
+      </c>
+      <c r="J71" t="n">
+        <v>8365.049956813673</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="F72" t="n">
+        <v>971.5584414151699</v>
+      </c>
+      <c r="G72" t="n">
+        <v>28</v>
+      </c>
+      <c r="H72" t="n">
+        <v>23</v>
+      </c>
+      <c r="I72" t="n">
+        <v>27203.63635962476</v>
+      </c>
+      <c r="J72" t="n">
+        <v>22345.84415254891</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>康复理疗</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="F73" t="n">
+        <v>640.743734376803</v>
+      </c>
+      <c r="G73" t="n">
+        <v>28</v>
+      </c>
+      <c r="H73" t="n">
+        <v>23</v>
+      </c>
+      <c r="I73" t="n">
+        <v>17940.82456255048</v>
+      </c>
+      <c r="J73" t="n">
+        <v>14737.10589066647</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7221</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1329.079953752674</v>
+      </c>
+      <c r="G74" t="n">
+        <v>20</v>
+      </c>
+      <c r="H74" t="n">
+        <v>16</v>
+      </c>
+      <c r="I74" t="n">
+        <v>26581.59907505348</v>
+      </c>
+      <c r="J74" t="n">
+        <v>21265.27926004279</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7221</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3550.416753774768</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="n">
+        <v>16</v>
+      </c>
+      <c r="I75" t="n">
+        <v>71008.33507549536</v>
+      </c>
+      <c r="J75" t="n">
+        <v>56806.66806039629</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>日间照料</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7221</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2341.503292477173</v>
+      </c>
+      <c r="G76" t="n">
+        <v>20</v>
+      </c>
+      <c r="H76" t="n">
+        <v>16</v>
+      </c>
+      <c r="I76" t="n">
+        <v>46830.06584954346</v>
+      </c>
+      <c r="J76" t="n">
+        <v>37464.05267963477</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>464</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="F77" t="n">
+        <v>85.40272795197905</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>683.2218236158324</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>464</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="F78" t="n">
+        <v>228.139229158218</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1825.113833265744</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>紧急救助</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>464</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="F79" t="n">
+        <v>150.4580428900995</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1203.664343120796</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>服务覆盖率(等价人口)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.8622496871148532</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>人口加权平均满意度</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8755101126271245</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>等价覆盖老人数量</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6534.990378643472</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>总老人数量</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7579</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>覆盖月需求</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>建设成本</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>利用率方差</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>站点方案</t>
+      <c r="B6" t="n">
+        <v>209999.793786773</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>总月需求</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>244931</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>需求覆盖率</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8573834826411233</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>完全覆盖小区数</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>部分覆盖小区数</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>未覆盖小区数</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总建设成本</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1180000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总日服务能力</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总日需求</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8164.366666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>总日已分配需求</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6999.993126225765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>最大利用率</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>站点数量</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>小型数量</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>中型数量</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>大型数量</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.8432026452527162</v>
-      </c>
-      <c r="D2" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>G:大型;I:中型;J:中型</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>建站位置假设</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>不允许任意地点建站，仅允许在10个小区候选点中选择建站。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.842144544166273</v>
-      </c>
-      <c r="D3" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>G:中型;I:大型;J:中型</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>需求分配假设</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>允许一个小区的日均服务需求按比例拆分给多个服务半径内的服务站。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.840642418516769</v>
-      </c>
-      <c r="D4" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>E:中型;G:大型;J:中型</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>覆盖率定义</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>若某小区只满足部分需求，则按“已满足需求/总需求”的比例折算等价覆盖老人数量。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8394898441190364</v>
-      </c>
-      <c r="D5" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>B:中型;G:大型;I:中型</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>价格满意度</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>问题2不调整服务价格，沿用附件2基准价格，因此价格满意度S3取1.00。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.839140292867265</v>
-      </c>
-      <c r="D6" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>E:中型;I:大型;J:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.8384317430325933</v>
-      </c>
-      <c r="D7" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>B:中型;G:中型;I:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.8369296173830894</v>
-      </c>
-      <c r="D8" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>B:中型;E:中型;G:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.8368020784128485</v>
-      </c>
-      <c r="D9" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>C:中型;G:大型;J:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8361360415682572</v>
-      </c>
-      <c r="D10" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>D:中型;G:大型;J:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8357770429853567</v>
-      </c>
-      <c r="D11" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>G:大型;H:中型;I:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8357770429853567</v>
-      </c>
-      <c r="D12" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>D:中型;G:大型;I:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.8354274917335853</v>
-      </c>
-      <c r="D13" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>B:中型;E:中型;I:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.8352999527633445</v>
-      </c>
-      <c r="D14" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>C:中型;I:大型;J:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.8347189418989136</v>
-      </c>
-      <c r="D15" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>G:中型;H:中型;I:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.8347189418989136</v>
-      </c>
-      <c r="D16" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D:中型;G:中型;I:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.834633915918753</v>
-      </c>
-      <c r="D17" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>D:中型;I:大型;J:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.8332168162494096</v>
-      </c>
-      <c r="D18" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>D:中型;E:中型;G:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.8332168162494096</v>
-      </c>
-      <c r="D19" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>E:中型;G:大型;H:中型</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.8330892772791687</v>
-      </c>
-      <c r="D20" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.0001012057064471878</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>B:中型;C:中型;G:大型</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>6351</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.8329617383089279</v>
-      </c>
-      <c r="D21" t="n">
-        <v>206806</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.0001012057064471879</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>F:中型;G:大型;J:中型</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>优化方法</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>使用简化混合整数线性规划MILP，分层优化：覆盖人口→距离价格满意度→需求覆盖→建设成本→最大利用率；最终按实际利用率复核响应满意度S2。</t>
         </is>
       </c>
     </row>
@@ -1814,7 +4614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,68 +4650,90 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>日实际服务量</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>利用率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>响应满意度S2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大型</t>
+          <t>小型</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>450000</v>
+        <v>180000</v>
       </c>
       <c r="D2" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E2" t="n">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="n">
-        <v>1606000</v>
+        <v>730000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9869111111111111</v>
+        <v>999.999018032304</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.999999018032304</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中型</t>
+          <t>小型</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>320000</v>
+        <v>180000</v>
       </c>
       <c r="D3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3" t="n">
         <v>2000</v>
       </c>
-      <c r="E3" t="n">
-        <v>3200</v>
-      </c>
       <c r="F3" t="n">
-        <v>1168000</v>
+        <v>730000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9710666666666666</v>
+        <v>999.999018032304</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.999999018032304</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1932,7 +4754,79 @@
         <v>1168000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9953333333333333</v>
+        <v>1999.998036064333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999990180321666</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>730000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>999.9990180321349</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.999999018032135</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>320000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1168000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1999.998036064688</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -1946,7 +4840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,27 +4866,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>分配服务站</t>
+          <t>日已分配需求</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>距离</t>
+          <t>日未满足需求</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>距离满意度</t>
+          <t>需求满足比例</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>响应满意度</t>
+          <t>等价覆盖老人数量</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>价格满意度</t>
+          <t>分配服务站及比例</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -2002,7 +4896,17 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>是否被覆盖</t>
+          <t>是否完全覆盖</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>是否部分覆盖</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>是否未覆盖</t>
         </is>
       </c>
     </row>
@@ -2021,29 +4925,35 @@
       <c r="D2" t="n">
         <v>857.3</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
+      <c r="E2" t="n">
+        <v>857.2991581590942</v>
       </c>
       <c r="F2" t="n">
-        <v>500</v>
+        <v>0.0008418409057640019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>0.9999990180323041</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
+        <v>785.999228173391</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A(100.0%)</t>
+        </is>
       </c>
       <c r="J2" t="n">
-        <v>0.86</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2060,29 +4970,35 @@
       <c r="D3" t="n">
         <v>715.7666666666667</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="E3" t="n">
+        <v>715.7666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
+        <v>671</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>J(100.0%)</t>
+        </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2099,27 +5015,33 @@
       <c r="D4" t="n">
         <v>1133.366666666667</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>700</v>
+        <v>1133.366666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2138,25 +5060,33 @@
       <c r="D5" t="n">
         <v>618.8</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>618.8000000011729</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
+        <v>601</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>H(100.0%)</t>
+        </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.880000000001668</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2175,29 +5105,35 @@
       <c r="D6" t="n">
         <v>954.1333333333333</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="E6" t="n">
+        <v>954.1333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
+        <v>866</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>E(100.0%)</t>
+        </is>
       </c>
       <c r="J6" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2214,22 +5150,22 @@
       <c r="D7" t="n">
         <v>515.5333333333333</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="E7" t="n">
+        <v>515.5328270709776</v>
       </c>
       <c r="F7" t="n">
-        <v>500</v>
+        <v>0.0005062623556568724</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9</v>
+        <v>0.999999017983275</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
+        <v>520.9994883692863</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>G(91.1%)、E(8.9%)</t>
+        </is>
       </c>
       <c r="J7" t="n">
         <v>0.86</v>
@@ -2237,6 +5173,12 @@
       <c r="K7" t="n">
         <v>1</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2253,28 +5195,34 @@
       <c r="D8" t="n">
         <v>1056.2</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
+      <c r="E8" t="n">
+        <v>1025.400052241088</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>30.79994775891214</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.9708389057385797</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I8" t="n">
+        <v>926.180316074605</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>G(97.1%)</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2292,25 +5240,33 @@
       <c r="D9" t="n">
         <v>652.0333333333333</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>652.0333333333011</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.217337507521734e-11</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.9999999999999507</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
+        <v>626.9999999999691</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>J(100.0%)</t>
+        </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2329,28 +5285,34 @@
       <c r="D10" t="n">
         <v>885.9333333333333</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
+      <c r="E10" t="n">
+        <v>885.7277554196353</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.2055779136979936</v>
       </c>
       <c r="G10" t="n">
+        <v>0.9997679532917849</v>
+      </c>
+      <c r="H10" t="n">
+        <v>812.8113460262211</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>G(57.0%)、J(43.0%)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8599999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2368,28 +5330,34 @@
       <c r="D11" t="n">
         <v>775.3</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="E11" t="n">
+        <v>775.3000000004955</v>
       </c>
       <c r="F11" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
+        <v>724</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>H(49.2%)、J(32.4%)、A(18.4%)</t>
+        </is>
       </c>
       <c r="J11" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.8763188479336668</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2403,111 +5371,685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>站点</t>
+          <t>小区</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>覆盖小区</t>
+          <t>服务站</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>覆盖老人总数</t>
+          <t>服务站规模</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>覆盖月需求</t>
+          <t>日分配需求</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>覆盖日需求</t>
+          <t>月分配需求</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>利用率</t>
+          <t>占本小区需求比例</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>等价覆盖老人数量</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>距离</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>距离满意度S1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>服务站实际利用率</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>响应满意度S2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>价格满意度S3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>综合满意度S</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>E、J、B、F</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2782</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>88822</v>
+        <v>857.2991581590942</v>
       </c>
       <c r="E2" t="n">
-        <v>2960.733333333333</v>
+        <v>25718.97474477283</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9869111111111111</v>
+        <v>0.9999990180323041</v>
+      </c>
+      <c r="G2" t="n">
+        <v>785.999228173391</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.999999018032304</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G、I</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1767</v>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>58264</v>
+        <v>715.7666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>1942.133333333333</v>
+        <v>21473</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9710666666666666</v>
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>671</v>
+      </c>
+      <c r="H3" t="n">
+        <v>300</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>618.8000000011729</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18564.00000003519</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.000000000001895</v>
+      </c>
+      <c r="G4" t="n">
+        <v>601.0000000011391</v>
+      </c>
+      <c r="H4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.999999018032135</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>954.1333333333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28624</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>866</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.999999018032304</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>45.86568469897068</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1375.97054096912</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08896744736642444</v>
+      </c>
+      <c r="G6" t="n">
+        <v>46.35204007790713</v>
+      </c>
+      <c r="H6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.999999018032304</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>469.667142372007</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14090.01427116021</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9110315706168506</v>
+      </c>
+      <c r="G7" t="n">
+        <v>474.6474482913791</v>
+      </c>
+      <c r="H7" t="n">
+        <v>500</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9999990180321666</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1025.400052241088</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30762.00156723264</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9708389057385797</v>
+      </c>
+      <c r="G8" t="n">
+        <v>926.180316074605</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9999990180321666</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C、A</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1802</v>
-      </c>
-      <c r="D4" t="n">
-        <v>59720</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1990.666666666667</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9953333333333333</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>652.0333333333011</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19560.99999999903</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9999999999999507</v>
+      </c>
+      <c r="G9" t="n">
+        <v>626.9999999999691</v>
+      </c>
+      <c r="H9" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>504.9308414512383</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15147.92524353715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5699422546292855</v>
+      </c>
+      <c r="G10" t="n">
+        <v>463.3630530136091</v>
+      </c>
+      <c r="H10" t="n">
+        <v>400</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9999990180321666</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>380.7969139683969</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11423.90741905191</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4298256986624994</v>
+      </c>
+      <c r="G11" t="n">
+        <v>349.448293012612</v>
+      </c>
+      <c r="H11" t="n">
+        <v>400</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>142.6998598732098</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4280.995796196295</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1840576033447824</v>
+      </c>
+      <c r="G12" t="n">
+        <v>133.2577048216225</v>
+      </c>
+      <c r="H12" t="n">
+        <v>500</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.999999018032304</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>小型</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>381.1990180309621</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11435.97054092886</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4916793731858147</v>
+      </c>
+      <c r="G13" t="n">
+        <v>355.9758661865299</v>
+      </c>
+      <c r="H13" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.999999018032135</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>251.4011220963235</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7542.033662889707</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.324263023470042</v>
+      </c>
+      <c r="G14" t="n">
+        <v>234.7664289923104</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -2521,7 +6063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2532,122 +6074,168 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>年度收入</t>
+          <t>覆盖小区及比例</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>年直接支出</t>
+          <t>等价覆盖老人总数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>年固定管理成本</t>
+          <t>覆盖月需求</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>建设成本</t>
+          <t>覆盖日需求</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>年折旧</t>
+          <t>利用率</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>运营利润</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>含折旧利润</t>
+          <t>响应满意度S2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>17368933.79651163</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A(100.0%)、J(18.4%)</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>14121775.43023256</v>
+        <v>919.2569329950135</v>
       </c>
       <c r="D2" t="n">
-        <v>1606000</v>
+        <v>29999.97054096912</v>
       </c>
       <c r="E2" t="n">
-        <v>450000</v>
+        <v>999.999018032304</v>
       </c>
       <c r="F2" t="n">
-        <v>22500</v>
+        <v>0.999999018032304</v>
       </c>
       <c r="G2" t="n">
-        <v>1641158.366279069</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1618658.366279069</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11393388.56049125</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E(100.0%)、F(8.9%)</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>9263370.827802457</v>
+        <v>912.3520400779071</v>
       </c>
       <c r="D3" t="n">
-        <v>1168000</v>
+        <v>29999.97054096912</v>
       </c>
       <c r="E3" t="n">
-        <v>320000</v>
+        <v>999.999018032304</v>
       </c>
       <c r="F3" t="n">
-        <v>16000</v>
+        <v>0.999999018032304</v>
       </c>
       <c r="G3" t="n">
-        <v>962017.7326887902</v>
-      </c>
-      <c r="H3" t="n">
-        <v>946017.7326887902</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F(91.1%)、G(97.1%)、I(57.0%)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1864.190817379593</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59999.94108193</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1999.998036064333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9999990180321666</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D(100.0%)、J(49.2%)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>956.975866187669</v>
+      </c>
+      <c r="D5" t="n">
+        <v>29999.97054096405</v>
+      </c>
+      <c r="E5" t="n">
+        <v>999.9990180321349</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.999999018032135</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>11678105.94591064</v>
-      </c>
-      <c r="C4" t="n">
-        <v>9494859.704729553</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1168000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>320000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1015246.241181083</v>
-      </c>
-      <c r="H4" t="n">
-        <v>999246.241181083</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B(100.0%)、H(100.0%)、I(43.0%)、J(32.4%)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1882.214722004891</v>
+      </c>
+      <c r="D6" t="n">
+        <v>59999.94108194065</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1999.998036064688</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9999990180323441</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -2661,159 +6249,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>站点</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>年度收入</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>年直接支出</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>年固定管理成本</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>建设成本</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>年折旧</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>运营利润</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>含折旧利润</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>服务覆盖率</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8379733474073097</v>
+        <v>5869358.970640854</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4770641.199553721</v>
+      </c>
+      <c r="D2" t="n">
+        <v>730000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>368717.7710871333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>359717.7710871333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>人口加权平均满意度</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8432026452527162</v>
+        <v>5882099.588232355</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4781449.801209992</v>
+      </c>
+      <c r="D3" t="n">
+        <v>730000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>370649.7870223634</v>
+      </c>
+      <c r="H3" t="n">
+        <v>361649.7870223634</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>被覆盖老人数量</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6351</v>
+        <v>11725199.41022405</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9533254.617162131</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1168000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1023944.793061921</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1007944.793061921</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>总老人数量</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7579</v>
+        <v>5842252.372305126</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4752918.484621574</v>
+      </c>
+      <c r="D5" t="n">
+        <v>730000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>359333.8876835518</v>
+      </c>
+      <c r="H5" t="n">
+        <v>350333.8876835518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>覆盖月需求</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206806</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>总月需求</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>244931</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>需求覆盖率</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8443439172664955</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>总建设成本</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1090000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>总日服务能力</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>总日需求</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>8164.366666666667</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>站点数量</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>小型数量</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>中型数量</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>大型数量</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
+        <v>11708621.41975062</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9522294.686332926</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1168000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1018326.733417694</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1002326.733417694</v>
       </c>
     </row>
   </sheetData>
